--- a/OpticalRx/Fabrication/PickAndPlace_XY_OpticalInOut.xlsx
+++ b/OpticalRx/Fabrication/PickAndPlace_XY_OpticalInOut.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="242">
   <si>
     <t xml:space="preserve">Designator</t>
   </si>
@@ -695,6 +695,57 @@
   </si>
   <si>
     <t xml:space="preserve"> SMD2520-4P                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q10                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q11                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q12                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q9                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">R102                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">R103                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">R104                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">R105                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">R106                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">R107                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">R108                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">R109                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">J6                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMD-1D25-4P-DEG0          </t>
   </si>
 </sst>
 </file>
@@ -709,6 +760,7 @@
       <sz val="10"/>
       <name val="DejaVu Sans"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -773,7 +825,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -900,10 +952,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G194"/>
+  <dimension ref="A1:G207"/>
   <sheetFormatPr defaultColWidth="10.08203125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="10.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.22"/>
@@ -5371,6 +5423,302 @@
         <v>9</v>
       </c>
     </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B195" s="1" t="n">
+        <v>34.941</v>
+      </c>
+      <c r="C195" s="1" t="n">
+        <v>10.286</v>
+      </c>
+      <c r="D195" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B196" s="1" t="n">
+        <v>44.841</v>
+      </c>
+      <c r="C196" s="1" t="n">
+        <v>10.186</v>
+      </c>
+      <c r="D196" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B197" s="1" t="n">
+        <v>55.041</v>
+      </c>
+      <c r="C197" s="1" t="n">
+        <v>10.186</v>
+      </c>
+      <c r="D197" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G197" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B198" s="1" t="n">
+        <v>24.941</v>
+      </c>
+      <c r="C198" s="1" t="n">
+        <v>10.286</v>
+      </c>
+      <c r="D198" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B199" s="1" t="n">
+        <v>20.495</v>
+      </c>
+      <c r="C199" s="1" t="n">
+        <v>3.405</v>
+      </c>
+      <c r="D199" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B200" s="1" t="n">
+        <v>30.595</v>
+      </c>
+      <c r="C200" s="1" t="n">
+        <v>3.405</v>
+      </c>
+      <c r="D200" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B201" s="1" t="n">
+        <v>40.595</v>
+      </c>
+      <c r="C201" s="1" t="n">
+        <v>3.405</v>
+      </c>
+      <c r="D201" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G201" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B202" s="1" t="n">
+        <v>50.595</v>
+      </c>
+      <c r="C202" s="1" t="n">
+        <v>3.405</v>
+      </c>
+      <c r="D202" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B203" s="1" t="n">
+        <v>24.805</v>
+      </c>
+      <c r="C203" s="1" t="n">
+        <v>6.505</v>
+      </c>
+      <c r="D203" s="1" t="n">
+        <v>270</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B204" s="1" t="n">
+        <v>37.995</v>
+      </c>
+      <c r="C204" s="1" t="n">
+        <v>12.295</v>
+      </c>
+      <c r="D204" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B205" s="1" t="n">
+        <v>48.195</v>
+      </c>
+      <c r="C205" s="1" t="n">
+        <v>12.295</v>
+      </c>
+      <c r="D205" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B206" s="1" t="n">
+        <v>58.505</v>
+      </c>
+      <c r="C206" s="1" t="n">
+        <v>10.305</v>
+      </c>
+      <c r="D206" s="1" t="n">
+        <v>270</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B207" s="1" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="C207" s="1" t="n">
+        <v>7.855</v>
+      </c>
+      <c r="D207" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
